--- a/app/templates/xlsx/daily_section.xlsx
+++ b/app/templates/xlsx/daily_section.xlsx
@@ -143,7 +143,28 @@
     <t xml:space="preserve">قریه </t>
   </si>
   <si>
-    <t xml:space="preserve">نمبر تذکره الکترونیکی</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">نمبر تذکره </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">الکترونیکی</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">صکوک</t>
@@ -306,15 +327,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -331,6 +344,14 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -434,15 +455,15 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -546,9 +567,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>233640</xdr:colOff>
+      <xdr:colOff>232920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>246240</xdr:rowOff>
+      <xdr:rowOff>245520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -562,7 +583,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2568960" y="254880"/>
-          <a:ext cx="994680" cy="982080"/>
+          <a:ext cx="993960" cy="981360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -583,9 +604,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>27720</xdr:colOff>
+      <xdr:colOff>27000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>210240</xdr:rowOff>
+      <xdr:rowOff>209520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -599,7 +620,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6333840" y="250560"/>
-          <a:ext cx="856800" cy="950400"/>
+          <a:ext cx="856080" cy="949680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1115,7 +1136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="87.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>23</v>
@@ -1159,7 +1180,7 @@
       <c r="S9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="9" t="s">
         <v>32</v>
       </c>
       <c r="U9" s="6" t="s">
@@ -1192,55 +1213,55 @@
       <c r="AG9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="98.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="R10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="10" t="s">
         <v>56</v>
       </c>
       <c r="T10" s="12" t="s">
@@ -1250,25 +1271,25 @@
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
-      <c r="Y10" s="9" t="s">
+      <c r="Y10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="Z10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AA10" s="9" t="s">
+      <c r="AA10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AB10" s="9" t="s">
+      <c r="AB10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AC10" s="9" t="s">
+      <c r="AC10" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AD10" s="9" t="s">
+      <c r="AD10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AE10" s="9" t="s">
+      <c r="AE10" s="10" t="s">
         <v>64</v>
       </c>
       <c r="AG10" s="1"/>

--- a/app/templates/xlsx/daily_section.xlsx
+++ b/app/templates/xlsx/daily_section.xlsx
@@ -44,28 +44,7 @@
     <t xml:space="preserve">مدیریت عمومی تدریسی  </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">جدول شهرت مکمل جدیدالشمولان سمستربهاری انستیتوت تکنالوژی کمپیوتر بخش روزانه سال </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="B Nazanin"/>
-        <family val="0"/>
-        <charset val="178"/>
-      </rPr>
-      <t xml:space="preserve">1405 </t>
-    </r>
+    <t xml:space="preserve">title</t>
   </si>
   <si>
     <t xml:space="preserve">ملاحظات </t>
@@ -270,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,17 +292,9 @@
       <b val="true"/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="B Nazanin"/>
+      <name val="Noto Naskh Arabic"/>
       <family val="0"/>
-      <charset val="178"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -366,19 +337,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -435,35 +399,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -567,9 +531,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>232920</xdr:colOff>
+      <xdr:colOff>231840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>245520</xdr:rowOff>
+      <xdr:rowOff>244440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -583,7 +547,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2568960" y="254880"/>
-          <a:ext cx="993960" cy="981360"/>
+          <a:ext cx="992880" cy="980280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -604,9 +568,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>27000</xdr:colOff>
+      <xdr:colOff>25920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>209520</xdr:rowOff>
+      <xdr:rowOff>208440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -620,7 +584,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6333840" y="250560"/>
-          <a:ext cx="856080" cy="949680"/>
+          <a:ext cx="855000" cy="948600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1037,7 +1001,7 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
